--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno1/anno1_task3_question_quality.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno1/anno1_task3_question_quality.xlsx
@@ -1,34 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AB8852-2593-43D8-95E7-9B8E8CC12167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\RLHF\phases\phase2\hh-annotations\results\kallirroi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419BE1D9-2D2B-4726-90F3-681FD0DD55C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="158">
   <si>
     <t>UID</t>
   </si>
@@ -69,46 +61,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000077-0003</t>
-  </si>
-  <si>
-    <t>I didn't know there were so many different regions and cultures in Japan.</t>
-  </si>
-  <si>
-    <t>Have you researched which regions you want to visit?</t>
-  </si>
-  <si>
-    <t>Have you considered visiting different regions during your trip?</t>
-  </si>
-  <si>
-    <t>Have you looked into any specific regions or cities you want to visit?</t>
-  </si>
-  <si>
-    <t>Which regions are you planning to visit?</t>
-  </si>
-  <si>
-    <t>Do you have any specific places you want to visit in Japan?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000153-0003</t>
-  </si>
-  <si>
-    <t>I'm worried my scrapbook won't be as good as some of the ones I've seen online.</t>
-  </si>
-  <si>
-    <t>Have you considered adding your own personal touch to the design?</t>
-  </si>
-  <si>
-    <t>What kind of materials or embellishments are you planning on using?</t>
-  </si>
-  <si>
-    <t>Have you considered any unique embellishments or materials you could add?</t>
-  </si>
-  <si>
-    <t>Have you thought about what type of scrapbooking supplies you want to use?</t>
-  </si>
-  <si>
-    <t>What's your favorite memory from last summer that you're hoping to include in your scrapbook?</t>
+    <t>SFTANNO-000059-0003</t>
+  </si>
+  <si>
+    <t>I'm considering a career change. I'm surprised at how open I am to new possibilities.</t>
+  </si>
+  <si>
+    <t>Have you started researching or networking in your new field?</t>
+  </si>
+  <si>
+    <t>Have you thought about the steps involved in making this change?</t>
+  </si>
+  <si>
+    <t>Have you thought about how you'll make the transition?</t>
+  </si>
+  <si>
+    <t>Have you considered any specific new fields or industries?</t>
+  </si>
+  <si>
+    <t>Have you thought about what kind of career path you'd like to explore?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000121-0003</t>
+  </si>
+  <si>
+    <t>The most challenging part was the uncertainty of waiting and not knowing if my paper would be accepted or not.</t>
+  </si>
+  <si>
+    <t>Have you thought about submitting your work to any other journals?</t>
+  </si>
+  <si>
+    <t>Have you considered submitting to other journals?</t>
+  </si>
+  <si>
+    <t>Do you have any upcoming research projects?</t>
+  </si>
+  <si>
+    <t>Do you have any advice for someone going through the publication process?</t>
+  </si>
+  <si>
+    <t>Have you considered publishing in an open-access journal?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0003</t>
@@ -174,46 +166,43 @@
     <t>Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000131-0003</t>
-  </si>
-  <si>
-    <t>I've always dreamed of visiting Japan, but I'm afraid of the language barrier.</t>
-  </si>
-  <si>
-    <t>Have you considered learning some basic Japanese phrases?</t>
-  </si>
-  <si>
-    <t>Have you looked into any cultural exchange programs?</t>
-  </si>
-  <si>
-    <t>Any other destinations you're interested in?</t>
-  </si>
-  <si>
-    <t>Have you started planning your itinerary?</t>
-  </si>
-  <si>
-    <t>Have you researched any cultural experiences you'd like to have?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000058-0003</t>
-  </si>
-  <si>
-    <t>I heard a rumor that the COVID-19 vaccine makes you infertile, is that true?</t>
-  </si>
-  <si>
-    <t>How can we help people separate fact from fiction?</t>
-  </si>
-  <si>
-    <t>Where did you hear that rumor?</t>
-  </si>
-  <si>
-    <t>Do you have any other questions about the vaccine?</t>
-  </si>
-  <si>
-    <t>Do you have any tips on how to combat misinformation?</t>
-  </si>
-  <si>
-    <t>Have you considered getting vaccinated?</t>
+    <t>SFTANNO-000100-0003</t>
+  </si>
+  <si>
+    <t>Look at all these vintage arcade games! I didn't expect to see so many.</t>
+  </si>
+  <si>
+    <t>Do you want to try playing any of them?</t>
+  </si>
+  <si>
+    <t>Do you want to play any of the vintage games?</t>
+  </si>
+  <si>
+    <t>Which game would you like to play next?</t>
+  </si>
+  <si>
+    <t>Do you want to try any of the vintage games?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000057-0003</t>
+  </si>
+  <si>
+    <t>I've been practicing mindfulness meditation and it's been a really positive experience.</t>
+  </si>
+  <si>
+    <t>Have you found any particular techniques or apps that you like?</t>
+  </si>
+  <si>
+    <t>How long have you been practicing, and what inspired you to start?</t>
+  </si>
+  <si>
+    <t>Have you noticed any specific benefits or changes in your daily life since starting?</t>
+  </si>
+  <si>
+    <t>Have you noticed any changes in your daily life or outlook since practicing mindfulness?</t>
+  </si>
+  <si>
+    <t>Have you tried any other forms of meditation or mindfulness practices?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0003</t>
@@ -237,145 +226,151 @@
     <t>Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000098-0003</t>
-  </si>
-  <si>
-    <t>Have you ever ridden in an autonomous vehicle before?</t>
-  </si>
-  <si>
-    <t>Do you think you would be interested in taking a ride in one sometime?</t>
-  </si>
-  <si>
-    <t>Would you be open to trying it out sometime?</t>
-  </si>
-  <si>
-    <t>Have you ever tried any other autonomous technologies, like self-driving cars?</t>
-  </si>
-  <si>
-    <t>What do you think it would be like to ride in an autonomous vehicle?</t>
-  </si>
-  <si>
-    <t>Would you be interested in trying one out?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000050-0003</t>
-  </si>
-  <si>
-    <t>I'm open to anything at this point.</t>
-  </si>
-  <si>
-    <t>Have you thought about any specific companies you'd like to work for?</t>
-  </si>
-  <si>
-    <t>Have you thought about reaching out to any recruiters?</t>
-  </si>
-  <si>
-    <t>Have you thought about reaching out to any old colleagues or contacts for job leads?</t>
-  </si>
-  <si>
-    <t>Have you looked into any job boards or websites?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000078-0003</t>
-  </si>
-  <si>
-    <t>I'm worried about cultural misunderstandings when I visit my parents' homeland.</t>
-  </si>
-  <si>
-    <t>That's a great idea! What phrases or customs have you looked into so far?</t>
-  </si>
-  <si>
-    <t>Have you looked into any cultural exchange programs or language courses that could help you better understand the local culture?</t>
-  </si>
-  <si>
-    <t>Have you researched any cultural etiquette or customs that you should be aware of before your trip?</t>
-  </si>
-  <si>
-    <t>Have you looked into any language courses or resources to help with communication while traveling?</t>
-  </si>
-  <si>
-    <t>What are some specific things you're looking forward to experiencing in your parents' homeland?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000095-0003</t>
-  </si>
-  <si>
-    <t>Yes, I have. I was so frustrated that the seat was uncomfortable and the entertainment system was broken.</t>
-  </si>
-  <si>
-    <t>Do you have any tips for avoiding jet lag?</t>
-  </si>
-  <si>
-    <t>Have you ever tried any in-flight movies that you really enjoyed?</t>
-  </si>
-  <si>
-    <t>Have you ever flown with a layover?</t>
-  </si>
-  <si>
-    <t>Do you have any tips for surviving long-haul flights?</t>
-  </si>
-  <si>
-    <t>Do you prefer window or aisle seats?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000139-0003</t>
-  </si>
-  <si>
-    <t>I'm scared my children are spending too much time online.</t>
-  </si>
-  <si>
-    <t>Have you talked to your children about online safety?</t>
-  </si>
-  <si>
-    <t>Have you talked to them about online safety?</t>
-  </si>
-  <si>
-    <t>Have you talked to your kids about online safety and how to avoid dangers?</t>
-  </si>
-  <si>
-    <t>Have you considered setting up parental controls or online monitoring software?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000130-0003</t>
-  </si>
-  <si>
-    <t>One episode covered the injustices faced by indigenous communities in regard to traditional plant knowledge and genetics research.</t>
-  </si>
-  <si>
-    <t>Have you found any other resources that cover the intersection of plant genetics and social justice?</t>
-  </si>
-  <si>
-    <t>Do you have any recommendations for other podcasts or resources that cover similar topics?</t>
-  </si>
-  <si>
-    <t>What do you think can be done to improve the representation of indigenous voices in plant genetics research?</t>
-  </si>
-  <si>
-    <t>Do you know of any organizations that are working towards these goals?</t>
-  </si>
-  <si>
-    <t>What other topics do you think the podcast should cover?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000073-0003</t>
-  </si>
-  <si>
-    <t>I saw a video of a robot dancing and it was just strange to watch.</t>
-  </si>
-  <si>
-    <t>Do you think robots will ever be able to perfectly replicate human movement?</t>
-  </si>
-  <si>
-    <t>What other areas of our lives do you think robots could potentially take over?</t>
-  </si>
-  <si>
-    <t>Do you think robots could ever replicate the emotional connection we have with dance?</t>
-  </si>
-  <si>
-    <t>Do you think there should be regulations put in place for robots and their capabilities?</t>
-  </si>
-  <si>
-    <t>Have you ever interacted with a robot before?</t>
+    <t>SFTANNO-000074-0003</t>
+  </si>
+  <si>
+    <t>Did you know some astronauts experience a "pale blue dot" effect after seeing earth in space?</t>
+  </si>
+  <si>
+    <t>Do you think humans will ever be able to live on Mars?</t>
+  </si>
+  <si>
+    <t>What's your favorite space movie?</t>
+  </si>
+  <si>
+    <t>Have you ever imagined what it would be like to see the Earth from space?</t>
+  </si>
+  <si>
+    <t>Do you think we'll ever be able to sustain human life on other planets?</t>
+  </si>
+  <si>
+    <t>Do you think we'll ever be able to colonize other planets?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000039-0003</t>
+  </si>
+  <si>
+    <t>I got a promotion at work, but now I have to pay more in taxes!</t>
+  </si>
+  <si>
+    <t>Have you considered talking to a tax professional to see if there are any deductions you can claim to offset the higher taxes?</t>
+  </si>
+  <si>
+    <t>Have you considered talking to a financial advisor about how to manage your taxes with your new income?</t>
+  </si>
+  <si>
+    <t>Have you considered contributing to a tax-deferred retirement plan to save for the future?</t>
+  </si>
+  <si>
+    <t>Do you have any questions about your new tax situation?</t>
+  </si>
+  <si>
+    <t>Have you considered talking to a tax professional to see if there are any deductions or credits you can take advantage of?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000076-0003</t>
+  </si>
+  <si>
+    <t>I'm scared of the future of our society with all of the environmental issues.</t>
+  </si>
+  <si>
+    <t>Do you have any ideas on how individuals can make a difference in environmental protection?</t>
+  </si>
+  <si>
+    <t>What do you think is the most effective way to bring about change?</t>
+  </si>
+  <si>
+    <t>What do you think we can do as individuals to make a positive impact on the environment?</t>
+  </si>
+  <si>
+    <t>What do you think individuals can do to make a difference?</t>
+  </si>
+  <si>
+    <t>Do you think that we need to make any personal changes to reduce our impact on the environment?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000088-0003</t>
+  </si>
+  <si>
+    <t>Honestly, it was stressful at times, but overall it was a great experience.</t>
+  </si>
+  <si>
+    <t>Maybe someday I'll find the courage to join a team too.</t>
+  </si>
+  <si>
+    <t>Do you still play with friends or anything?</t>
+  </si>
+  <si>
+    <t>What made it worthwhile for you?</t>
+  </si>
+  <si>
+    <t>Do you still play basketball today?</t>
+  </si>
+  <si>
+    <t>What was your favorite part of playing on the team?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000115-0003</t>
+  </si>
+  <si>
+    <t>Not yet, but I'm open to suggestions.</t>
+  </si>
+  <si>
+    <t>Do you want me to send over some resources that might be helpful?</t>
+  </si>
+  <si>
+    <t>Do you want to try any of those suggestions together?</t>
+  </si>
+  <si>
+    <t>Have you considered reaching out to a professional for guidance?</t>
+  </si>
+  <si>
+    <t>What are some small self-care activities that you enjoy?</t>
+  </si>
+  <si>
+    <t>Have you considered trying a new hobby or activity to help with your feelings?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000109-0003</t>
+  </si>
+  <si>
+    <t>I would need some help actually. The grill is such a hassle to set up and I'm already getting overwhelmed.</t>
+  </si>
+  <si>
+    <t>Do you have any other food items you're planning on grilling?</t>
+  </si>
+  <si>
+    <t>Do you have any other drinks or snacks besides the food?</t>
+  </si>
+  <si>
+    <t>Is there anything else I can help with before we start grilling?</t>
+  </si>
+  <si>
+    <t>What kind of drinks do you have planned for the BBQ?</t>
+  </si>
+  <si>
+    <t>Do you need any help with anything else for the BBQ?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000068-0003</t>
+  </si>
+  <si>
+    <t>Ugh, I hate algebra.</t>
+  </si>
+  <si>
+    <t>Let's break it down and work through some problems together.</t>
+  </si>
+  <si>
+    <t>Have you considered finding a tutor or joining a study group?</t>
+  </si>
+  <si>
+    <t>Have you tried using any different study methods or resources to help with algebra?</t>
+  </si>
+  <si>
+    <t>Do you want to try working through some problems together?</t>
+  </si>
+  <si>
+    <t>Do you want to work on some real-life applications of algebra together?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0003</t>
@@ -396,46 +391,46 @@
     <t>Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000105-0003</t>
-  </si>
-  <si>
-    <t>I don't like this cold and gloomy weather.</t>
-  </si>
-  <si>
-    <t>Have you tried any indoor activities to lift your spirits?</t>
-  </si>
-  <si>
-    <t>What's your favorite thing to do on a cold day?</t>
-  </si>
-  <si>
-    <t>Have you tried any new indoor activities recently?</t>
-  </si>
-  <si>
-    <t>Have you ever tried indoor rock climbing?</t>
-  </si>
-  <si>
-    <t>What's your favorite way to spend a rainy day?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000154-0003</t>
-  </si>
-  <si>
-    <t>My partner keeps criticizing how I chop vegetables, it's driving me insane.</t>
-  </si>
-  <si>
-    <t>Have you tried watching cooking shows or reading recipes together to find a compromise?</t>
-  </si>
-  <si>
-    <t>Have you thought about trying a new recipe together?</t>
-  </si>
-  <si>
-    <t>Do you have any other cooking tips to share?</t>
-  </si>
-  <si>
-    <t>Have you tried talking to them about it?</t>
-  </si>
-  <si>
-    <t>Have you tried any new recipes lately?</t>
+    <t>SFTANNO-000092-0003</t>
+  </si>
+  <si>
+    <t>I used to love going out on my boat, but it's too expensive to maintain now.</t>
+  </si>
+  <si>
+    <t>Have you thought about selling it or finding someone who might be interested in buying it?</t>
+  </si>
+  <si>
+    <t>Have you thought about selling it or renting it out to help with the costs?</t>
+  </si>
+  <si>
+    <t>Have you considered selling your boat or renting one instead?</t>
+  </si>
+  <si>
+    <t>Have you considered selling your boat and using the money for other water activities?</t>
+  </si>
+  <si>
+    <t>Have you considered joining a boat club or co-op to save on costs?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000140-0003</t>
+  </si>
+  <si>
+    <t>I'm so frustrated that my computer keeps crashing.</t>
+  </si>
+  <si>
+    <t>Is there anything else I can help you with?</t>
+  </si>
+  <si>
+    <t>Have you checked the hard drive or RAM for any issues?</t>
+  </si>
+  <si>
+    <t>Have you considered taking your computer to a repair shop for a professional diagnosis?</t>
+  </si>
+  <si>
+    <t>Have you tried running a virus scan or updating your software?</t>
+  </si>
+  <si>
+    <t>Have you considered taking it to a professional for repair?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0003</t>
@@ -480,25 +475,25 @@
     <t>Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000118-0003</t>
-  </si>
-  <si>
-    <t>We can support local community clinics and increase our involvement in community-based programs that advocate for health equity.</t>
-  </si>
-  <si>
-    <t>What other initiatives can we support to promote health equity?</t>
-  </si>
-  <si>
-    <t>How can we continue to work towards making healthcare more accessible and equitable for all?</t>
-  </si>
-  <si>
-    <t>How can we encourage more people to get involved and support these initiatives?</t>
-  </si>
-  <si>
-    <t>What other ideas do you have to promote health equity at the local level?</t>
-  </si>
-  <si>
-    <t>What other initiatives can we take to support health equity in our communities?</t>
+    <t>SFTANNO-000069-0003</t>
+  </si>
+  <si>
+    <t>Yes, I love supporting Leave No Trace and the Sustainable Travel International.</t>
+  </si>
+  <si>
+    <t>Do you have any tips for sustainable camping practices?</t>
+  </si>
+  <si>
+    <t>Have you ever participated in any environmental conservation projects?</t>
+  </si>
+  <si>
+    <t>What's your favorite outdoor activity to do in your free time?</t>
+  </si>
+  <si>
+    <t>How can we encourage others to be more eco-conscious when enjoying the outdoors?</t>
+  </si>
+  <si>
+    <t>Do you have any favorite eco-friendly travel practices?</t>
   </si>
 </sst>
 </file>
@@ -517,7 +512,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -866,14 +860,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="2" customWidth="1"/>
-    <col min="2" max="13" width="27.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.6640625" style="2" customWidth="1"/>
+    <col min="2" max="13" width="28.33203125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -914,7 +908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -925,34 +919,34 @@
         <v>15</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -963,34 +957,34 @@
         <v>22</v>
       </c>
       <c r="D3" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1001,7 +995,7 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
@@ -1013,22 +1007,22 @@
         <v>31</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1039,34 +1033,34 @@
         <v>36</v>
       </c>
       <c r="D5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L5" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1083,28 +1077,28 @@
         <v>44</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1115,186 +1109,186 @@
         <v>50</v>
       </c>
       <c r="D7" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J7" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="2">
-        <v>4</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2">
+        <v>3</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="2">
-        <v>2</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="2">
-        <v>3</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="2">
-        <v>3</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="2">
-        <v>3</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="2">
-        <v>3</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2">
+        <v>3</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="2">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="2">
-        <v>4</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="2">
-        <v>2</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="L11" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>82</v>
       </c>
@@ -1311,7 +1305,7 @@
         <v>85</v>
       </c>
       <c r="F12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>86</v>
@@ -1323,16 +1317,16 @@
         <v>87</v>
       </c>
       <c r="J12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="L12" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>89</v>
       </c>
@@ -1343,13 +1337,13 @@
         <v>91</v>
       </c>
       <c r="D13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>93</v>
@@ -1361,16 +1355,16 @@
         <v>94</v>
       </c>
       <c r="J13" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="L13" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>96</v>
       </c>
@@ -1381,332 +1375,332 @@
         <v>98</v>
       </c>
       <c r="D14" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="F14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>101</v>
       </c>
       <c r="J14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L14" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H15" s="2">
         <v>4</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J15" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2">
         <v>2</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J16" s="2">
         <v>4</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L16" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="2">
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="2">
-        <v>4</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="2">
-        <v>5</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="J17" s="2">
         <v>2</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="2">
         <v>5</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F19" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H19" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J19" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L19" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F20" s="2">
         <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="2">
         <v>2</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L20" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F22" s="2">
         <v>2</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H22" s="2">
         <v>4</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L22" s="2">
         <v>5</v>
@@ -1714,7 +1708,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{FA946230-4A95-4C9A-8787-BDC0183F1EE5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J22 D2:D22 F2:F22 H2:H22 L2:L22" xr:uid="{819E2FF9-C952-4BEF-887D-1E408CF392DB}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
